--- a/etf_holdings/2026-09-21_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-21_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:34</t>
+          <t>2026-09-21 23:11:56</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:34</t>
+          <t>2026-09-21 23:11:56</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:34</t>
+          <t>2026-09-21 23:11:56</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:34</t>
+          <t>2026-09-21 23:11:56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:34</t>
+          <t>2026-09-21 23:11:56</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:34</t>
+          <t>2026-09-21 23:11:56</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:34</t>
+          <t>2026-09-21 23:11:56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:34</t>
+          <t>2026-09-21 23:11:56</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:34</t>
+          <t>2026-09-21 23:11:56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:34</t>
+          <t>2026-09-21 23:11:56</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:34</t>
+          <t>2026-09-21 23:11:56</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:34</t>
+          <t>2026-09-21 23:11:56</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:34</t>
+          <t>2026-09-21 23:11:56</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:34</t>
+          <t>2026-09-21 23:11:56</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:34</t>
+          <t>2026-09-21 23:11:56</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:45</t>
+          <t>2026-09-21 23:11:57</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:45</t>
+          <t>2026-09-21 23:11:57</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:45</t>
+          <t>2026-09-21 23:11:57</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:45</t>
+          <t>2026-09-21 23:11:57</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:45</t>
+          <t>2026-09-21 23:11:57</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:45</t>
+          <t>2026-09-21 23:11:57</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:45</t>
+          <t>2026-09-21 23:11:57</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:45</t>
+          <t>2026-09-21 23:11:57</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:45</t>
+          <t>2026-09-21 23:11:57</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:45</t>
+          <t>2026-09-21 23:11:57</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:45</t>
+          <t>2026-09-21 23:11:57</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:45</t>
+          <t>2026-09-21 23:11:57</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:45</t>
+          <t>2026-09-21 23:11:57</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:45</t>
+          <t>2026-09-21 23:11:57</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:45</t>
+          <t>2026-09-21 23:11:57</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:57</t>
+          <t>2026-09-21 23:11:59</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:57</t>
+          <t>2026-09-21 23:11:59</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:57</t>
+          <t>2026-09-21 23:11:59</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:57</t>
+          <t>2026-09-21 23:11:59</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:57</t>
+          <t>2026-09-21 23:11:59</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:57</t>
+          <t>2026-09-21 23:11:59</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:57</t>
+          <t>2026-09-21 23:11:59</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:57</t>
+          <t>2026-09-21 23:11:59</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:57</t>
+          <t>2026-09-21 23:11:59</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:57</t>
+          <t>2026-09-21 23:11:59</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:57</t>
+          <t>2026-09-21 23:11:59</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:57</t>
+          <t>2026-09-21 23:11:59</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:57</t>
+          <t>2026-09-21 23:11:59</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:57</t>
+          <t>2026-09-21 23:11:59</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-21 19:26:57</t>
+          <t>2026-09-21 23:11:59</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-21 19:27:08</t>
+          <t>2026-09-21 23:12:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-21 19:27:08</t>
+          <t>2026-09-21 23:12:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-21 19:27:08</t>
+          <t>2026-09-21 23:12:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-21 19:27:08</t>
+          <t>2026-09-21 23:12:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-21 19:27:08</t>
+          <t>2026-09-21 23:12:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-21_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-21_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:56</t>
+          <t>2026-09-21 23:19:20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:56</t>
+          <t>2026-09-21 23:19:20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:56</t>
+          <t>2026-09-21 23:19:20</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:56</t>
+          <t>2026-09-21 23:19:20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:56</t>
+          <t>2026-09-21 23:19:20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:56</t>
+          <t>2026-09-21 23:19:20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:56</t>
+          <t>2026-09-21 23:19:20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:56</t>
+          <t>2026-09-21 23:19:20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:56</t>
+          <t>2026-09-21 23:19:20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:56</t>
+          <t>2026-09-21 23:19:20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:56</t>
+          <t>2026-09-21 23:19:20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:56</t>
+          <t>2026-09-21 23:19:20</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:56</t>
+          <t>2026-09-21 23:19:20</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:56</t>
+          <t>2026-09-21 23:19:20</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:56</t>
+          <t>2026-09-21 23:19:20</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:57</t>
+          <t>2026-09-21 23:19:21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:57</t>
+          <t>2026-09-21 23:19:21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:57</t>
+          <t>2026-09-21 23:19:21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:57</t>
+          <t>2026-09-21 23:19:21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:57</t>
+          <t>2026-09-21 23:19:21</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:57</t>
+          <t>2026-09-21 23:19:21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:57</t>
+          <t>2026-09-21 23:19:21</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:57</t>
+          <t>2026-09-21 23:19:21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:57</t>
+          <t>2026-09-21 23:19:21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:57</t>
+          <t>2026-09-21 23:19:21</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:57</t>
+          <t>2026-09-21 23:19:21</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:57</t>
+          <t>2026-09-21 23:19:21</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:57</t>
+          <t>2026-09-21 23:19:21</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:57</t>
+          <t>2026-09-21 23:19:21</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:57</t>
+          <t>2026-09-21 23:19:21</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:59</t>
+          <t>2026-09-21 23:19:22</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:59</t>
+          <t>2026-09-21 23:19:22</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:59</t>
+          <t>2026-09-21 23:19:22</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:59</t>
+          <t>2026-09-21 23:19:22</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:59</t>
+          <t>2026-09-21 23:19:22</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:59</t>
+          <t>2026-09-21 23:19:22</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:59</t>
+          <t>2026-09-21 23:19:22</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:59</t>
+          <t>2026-09-21 23:19:22</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:59</t>
+          <t>2026-09-21 23:19:22</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:59</t>
+          <t>2026-09-21 23:19:22</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:59</t>
+          <t>2026-09-21 23:19:22</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:59</t>
+          <t>2026-09-21 23:19:22</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:59</t>
+          <t>2026-09-21 23:19:22</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:59</t>
+          <t>2026-09-21 23:19:22</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-21 23:11:59</t>
+          <t>2026-09-21 23:19:22</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-21 23:12:00</t>
+          <t>2026-09-21 23:19:23</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-21 23:12:00</t>
+          <t>2026-09-21 23:19:23</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-21 23:12:00</t>
+          <t>2026-09-21 23:19:23</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-21 23:12:00</t>
+          <t>2026-09-21 23:19:23</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-21 23:12:00</t>
+          <t>2026-09-21 23:19:23</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-21_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-21_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:20</t>
+          <t>2026-09-21 23:54:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>11.94%3,800,000</t>
+          <t>11.97%3,800,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>11.94%</t>
+          <t>11.97%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:20</t>
+          <t>2026-09-21 23:54:09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.25%13,800,000</t>
+          <t>9.04%13,800,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.25%</t>
+          <t>9.04%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:20</t>
+          <t>2026-09-21 23:54:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.62%1,380,000</t>
+          <t>8.58%1,380,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.62%</t>
+          <t>8.58%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:20</t>
+          <t>2026-09-21 23:54:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.98%500,000</t>
+          <t>8.13%500,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.98%</t>
+          <t>8.13%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:20</t>
+          <t>2026-09-21 23:54:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.50%1,080,000</t>
+          <t>6.87%1,080,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.50%</t>
+          <t>6.87%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:20</t>
+          <t>2026-09-21 23:54:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6.39%5,100,000</t>
+          <t>6.61%5,100,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6.39%</t>
+          <t>6.61%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:20</t>
+          <t>2026-09-21 23:54:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.47%1,250,000</t>
+          <t>5.42%1,250,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.47%</t>
+          <t>5.42%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:20</t>
+          <t>2026-09-21 23:54:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5.27%7,500,000</t>
+          <t>5.30%7,500,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.27%</t>
+          <t>5.30%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:20</t>
+          <t>2026-09-21 23:54:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8046南亞電路</t>
+          <t>3189景碩科技</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-3.64%1060</t>
+          <t>-0.6%827</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.64%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1060</v>
+        <v>827</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.63%3,300,000</t>
+          <t>4.46%4,250,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.63%</t>
+          <t>4.46%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3300000</v>
+        <v>4250000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:20</t>
+          <t>2026-09-21 23:54:09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3189景碩科技</t>
+          <t>8046南亞電路</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.6%827</t>
+          <t>-3.64%1060</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>-3.64%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>827</v>
+        <v>1060</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.51%4,250,000</t>
+          <t>4.44%3,300,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.51%</t>
+          <t>4.44%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>4250000</v>
+        <v>3300000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:20</t>
+          <t>2026-09-21 23:54:09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.46%140,500</t>
+          <t>3.54%140,500</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>3.54%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:20</t>
+          <t>2026-09-21 23:54:09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6223旺矽科技</t>
+          <t>3081聯亞光電</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-5.26%5495</t>
+          <t>-0.17%2875</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-5.26%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5495</v>
+        <v>2875</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.33%450,000</t>
+          <t>3.29%900,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.33%</t>
+          <t>3.29%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>450000</v>
+        <v>900000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:20</t>
+          <t>2026-09-21 23:54:09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3081聯亞光電</t>
+          <t>6223旺矽科技</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.17%2875</t>
+          <t>-5.26%5495</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-5.26%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2875</v>
+        <v>5495</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.31%900,000</t>
+          <t>3.14%450,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.31%</t>
+          <t>3.14%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>900000</v>
+        <v>450000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:20</t>
+          <t>2026-09-21 23:54:09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:20</t>
+          <t>2026-09-21 23:54:09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.75%2,700,000</t>
+          <t>2.71%2,700,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:21</t>
+          <t>2026-09-21 23:54:10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7769鴻勁精密</t>
+          <t>3653健策精密</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-8.26%6000</t>
+          <t>+4.8%5790</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-8.26%</t>
+          <t>+4.8%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>6000</v>
+        <v>5790</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.09%250,000</t>
+          <t>2.13%290,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>250000</v>
+        <v>290000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:21</t>
+          <t>2026-09-21 23:54:10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2303聯華電子</t>
+          <t>3711日月光投</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+0.64%157</t>
+          <t>+3.92%663</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+3.92%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>157</v>
+        <v>663</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.07%10,400,000</t>
+          <t>2.11%2,500,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>10400000</v>
+        <v>2500000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:21</t>
+          <t>2026-09-21 23:54:10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3653健策精密</t>
+          <t>2303聯華電子</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+4.8%5790</t>
+          <t>+0.64%157</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+4.8%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5790</v>
+        <v>157</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.05%290,000</t>
+          <t>2.07%10,400,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.07%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>290000</v>
+        <v>10400000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:21</t>
+          <t>2026-09-21 23:54:10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3711日月光投</t>
+          <t>2308台達電子</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+3.92%663</t>
+          <t>+8.07%1875</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+3.92%</t>
+          <t>+8.07%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>663</v>
+        <v>1875</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.04%2,500,000</t>
+          <t>2.07%871,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.07%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>2500000</v>
+        <v>871000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:21</t>
+          <t>2026-09-21 23:54:10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:21</t>
+          <t>2026-09-21 23:54:10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.01%850,000</t>
+          <t>1.99%850,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.99%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:21</t>
+          <t>2026-09-21 23:54:10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>0.01%1,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:21</t>
+          <t>2026-09-21 23:54:10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2382廣達電腦</t>
+          <t>7769鴻勁精密</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+0.44%344.5</t>
+          <t>-8.26%6000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>-8.26%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>344.5</v>
+        <v>6000</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>0.01%1,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:21</t>
+          <t>2026-09-21 23:54:10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,30 +1907,30 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2360致茂電子</t>
+          <t>8299群聯電子</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+3.71%2375</t>
+          <t>+0.47%2150</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+3.71%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2375</v>
+        <v>2150</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:21</t>
+          <t>2026-09-21 23:54:10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2317鴻海精密</t>
+          <t>6274台燿科技</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-0.2%250</t>
+          <t>+4.74%1435</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>+4.74%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>250</v>
+        <v>1435</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:21</t>
+          <t>2026-09-21 23:54:10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,34 +2029,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>5347世界先進</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+4.07%2300</t>
+          <t>0%172</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+4.07%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2300</v>
+        <v>172</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:21</t>
+          <t>2026-09-21 23:54:10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,30 +2090,30 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>8299群聯電子</t>
+          <t>3044健鼎科技</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+0.47%2150</t>
+          <t>+1.16%524</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2150</v>
+        <v>524</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:21</t>
+          <t>2026-09-21 23:54:10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,34 +2151,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2603長榮海運</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+0.62%242</t>
+          <t>+4.07%2300</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+0.62%</t>
+          <t>+4.07%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>242</v>
+        <v>2300</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:21</t>
+          <t>2026-09-21 23:54:10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,34 +2212,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2308台達電子</t>
+          <t>3231緯創資通</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+8.07%1875</t>
+          <t>0%186.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+8.07%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1875</v>
+        <v>186.5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:21</t>
+          <t>2026-09-21 23:54:10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,34 +2273,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3231緯創資通</t>
+          <t>1216統一企業</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0%186.5</t>
+          <t>-0.4%74.7</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>-0.4%</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0%1,000</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="H31" t="n">
-        <v>186.5</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>&lt;0.01%9,000</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>&lt;0.01%</t>
-        </is>
-      </c>
       <c r="K31" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:22</t>
+          <t>2026-09-21 23:54:12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,34 +2334,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>5347世界先進</t>
+          <t>3036文曄科技</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0%172</t>
+          <t>+0.49%206.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
+          <t>+0.49%</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>206.5</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0%1,000</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="H32" t="n">
-        <v>172</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>&lt;0.01%9,000</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>&lt;0.01%</t>
-        </is>
-      </c>
       <c r="K32" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:22</t>
+          <t>2026-09-21 23:54:12</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,30 +2395,30 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6274台燿科技</t>
+          <t>2412中華電信</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+4.74%1435</t>
+          <t>-0.69%144.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+4.74%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1435</v>
+        <v>144.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:22</t>
+          <t>2026-09-21 23:54:12</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,34 +2456,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2881富邦金融</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+2.66%154.5</t>
+          <t>+3.43%301.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+2.66%</t>
+          <t>+3.43%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>154.5</v>
+        <v>301.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>0%1,450</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>9000</v>
+        <v>1450</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:22</t>
+          <t>2026-09-21 23:54:12</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,34 +2517,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2882國泰金融</t>
+          <t>2357華碩電腦</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+2.26%113</t>
+          <t>-1.46%946</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>-1.46%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>113</v>
+        <v>946</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:22</t>
+          <t>2026-09-21 23:54:12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,30 +2578,30 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2357華碩電腦</t>
+          <t>2360致茂電子</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-1.46%946</t>
+          <t>+3.71%2375</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-1.46%</t>
+          <t>+3.71%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>946</v>
+        <v>2375</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:22</t>
+          <t>2026-09-21 23:54:12</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2657,12 +2657,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:22</t>
+          <t>2026-09-21 23:54:12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,34 +2700,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2885元大金融</t>
+          <t>2382廣達電腦</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.57%70.4</t>
+          <t>+0.44%344.5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.57%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>70.40000000000001</v>
+        <v>344.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,360</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>9360</v>
+        <v>9000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:22</t>
+          <t>2026-09-21 23:54:12</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2891中國信託</t>
+          <t>2313華通電腦</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+1.29%70.4</t>
+          <t>-2.84%222</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+1.29%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>70.40000000000001</v>
+        <v>222</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>0%1,253</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>9000</v>
+        <v>1253</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:22</t>
+          <t>2026-09-21 23:54:12</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,34 +2822,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3044健鼎科技</t>
+          <t>2317鴻海精密</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+1.16%524</t>
+          <t>-0.2%250</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+1.16%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>524</v>
+        <v>250</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:22</t>
+          <t>2026-09-21 23:54:12</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,30 +2883,30 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2886兆豐金融</t>
+          <t>2603長榮海運</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0%51.1</t>
+          <t>+0.62%242</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
+          <t>+0.62%</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>242</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>0%9,000</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
           <t>0%</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>51.1</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>&lt;0.01%9,000</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:22</t>
+          <t>2026-09-21 23:54:12</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2887台新新光</t>
+          <t>2880華南金融</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-1.35%43.8</t>
+          <t>-2.1%46.65</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-1.35%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>43.8</v>
+        <v>46.65</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>0%9,090</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>9000</v>
+        <v>9090</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:22</t>
+          <t>2026-09-21 23:54:12</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,30 +3005,30 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2890永豐金融</t>
+          <t>2881富邦金融</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+0.99%45.7</t>
+          <t>+2.66%154.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>+2.66%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>45.7</v>
+        <v>154.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:22</t>
+          <t>2026-09-21 23:54:12</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,34 +3066,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>2882國泰金融</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+3.43%301.5</t>
+          <t>+2.26%113</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+3.43%</t>
+          <t>+2.26%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>301.5</v>
+        <v>113</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,450</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>1450</v>
+        <v>9000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:22</t>
+          <t>2026-09-21 23:54:12</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,30 +3127,30 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2884玉山金融</t>
+          <t>2883凱基金融</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-0.43%46.2</t>
+          <t>+2.93%40.45</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-0.43%</t>
+          <t>+2.93%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>46.2</v>
+        <v>40.45</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:22</t>
+          <t>2026-09-21 23:54:12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,38 +3188,38 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2880華南金融</t>
+          <t>2884玉山金融</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-2.1%46.65</t>
+          <t>-0.43%46.2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>46.65</v>
+        <v>46.2</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,090</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>9090</v>
+        <v>9000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:23</t>
+          <t>2026-09-21 23:54:13</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,25 +3249,27 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2883凱基金融</t>
+          <t>2885元大金融</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+2.93%40.45</t>
+          <t>+0.57%70.4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+2.93%</t>
-        </is>
-      </c>
-      <c r="H47" t="n">
-        <v>40.45</v>
+          <t>+0.57%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>70.4</t>
+        </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>0%9,360</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3276,7 +3278,7 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>9000</v>
+        <v>9360</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -3297,7 +3299,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:23</t>
+          <t>2026-09-21 23:54:13</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,25 +3312,27 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2313華通電腦</t>
+          <t>2886兆豐金融</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-2.84%222</t>
+          <t>0%51.1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-2.84%</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
-        <v>222</v>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>51.1</t>
+        </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0%1,253</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3337,7 +3341,7 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>1253</v>
+        <v>9000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -3358,7 +3362,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:23</t>
+          <t>2026-09-21 23:54:13</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,25 +3375,27 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>3036文曄科技</t>
+          <t>2887台新新光</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+0.49%206.5</t>
+          <t>-1.35%43.8</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+0.49%</t>
-        </is>
-      </c>
-      <c r="H49" t="n">
-        <v>206.5</v>
+          <t>-1.35%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>43.8</t>
+        </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3398,7 +3404,7 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3419,7 +3425,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:23</t>
+          <t>2026-09-21 23:54:13</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,25 +3438,27 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2412中華電信</t>
+          <t>2890永豐金融</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-0.69%144.5</t>
+          <t>+0.99%45.7</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-0.69%</t>
-        </is>
-      </c>
-      <c r="H50" t="n">
-        <v>144.5</v>
+          <t>+0.99%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>45.7</t>
+        </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3459,7 +3467,7 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3480,7 +3488,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-21 23:19:23</t>
+          <t>2026-09-21 23:54:13</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,25 +3501,27 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1216統一企業</t>
+          <t>2891中國信託</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-0.4%74.7</t>
+          <t>+1.29%70.4</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-0.4%</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
-        <v>74.7</v>
+          <t>+1.29%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>70.4</t>
+        </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0%9,000</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3520,7 +3530,7 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
